--- a/teach/alunos/Paulo Panzo/Instrumentacão Controlo Angola.xlsx
+++ b/teach/alunos/Paulo Panzo/Instrumentacão Controlo Angola.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josej\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josej\Documents\Git\excel\teach\alunos\Paulo Panzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6350" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6374" uniqueCount="1224">
   <si>
     <t>Passo</t>
   </si>
@@ -3636,6 +3636,66 @@
   </si>
   <si>
     <t>Área para Tabelas Dinâmicas - Insira aqui os seus resumos</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Exercício</t>
+  </si>
+  <si>
+    <t>O que o aluno deve fazer</t>
+  </si>
+  <si>
+    <t>PROCV (VLOOKUP)</t>
+  </si>
+  <si>
+    <t>Pesquisa de Custo por ID</t>
+  </si>
+  <si>
+    <t>Na aba 'Tabelas_Dinamicas', use a função PROCV para encontrar o 'Custo_Estimado_AKZ' da Ordem de Manutenção MAN-150 consultando a aba 'Manutenção'.</t>
+  </si>
+  <si>
+    <t>Verificação de Estado de Ticket</t>
+  </si>
+  <si>
+    <t>A partir do ID 'REP-045', use o PROCV para descobrir qual foi a 'Peça_Substituída' na aba 'Reparação'.</t>
+  </si>
+  <si>
+    <t>Tabelas Dinâmicas</t>
+  </si>
+  <si>
+    <t>Resumo Financeiro por Província</t>
+  </si>
+  <si>
+    <t>Crie uma Tabela Dinâmica que mostre a soma do 'Custo_Estimado_AKZ' agrupado por 'Província'. Qual província teve o maior gasto?</t>
+  </si>
+  <si>
+    <t>Análise de Falhas Críticas</t>
+  </si>
+  <si>
+    <t>Crie uma Tabela Dinâmica que conte quantos equipamentos de cada 'Tipo_Equipamento' estão com o estado 'Em Atraso' na aba 'Manutenção'.</t>
+  </si>
+  <si>
+    <t>Gráficos</t>
+  </si>
+  <si>
+    <t>Distribuição de Manutenção</t>
+  </si>
+  <si>
+    <t>Gere um gráfico de 'Pizza' (Circular) baseado na Tabela Dinâmica de 'Estado' das manutenções.</t>
+  </si>
+  <si>
+    <t>Evolução de Custos de Reparação</t>
+  </si>
+  <si>
+    <t>Crie um gráfico de 'Colunas' que compare o 'Tempo_Paragem_Horas' médio por 'Prioridade' na aba 'Reparação'.</t>
+  </si>
+  <si>
+    <t>Desafio Final</t>
+  </si>
+  <si>
+    <t>Crie um pequeno Dashboard na aba 'Dashboard_Graficos' que combine 2 gráficos e 1 segmentação de dados (Slicer) por 'Unidade_Operacional'.</t>
   </si>
 </sst>
 </file>
@@ -3643,7 +3703,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -3703,16 +3763,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -4017,11 +4081,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="110.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="143.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4088,6 +4153,94 @@
       </c>
       <c r="C6" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1223</v>
       </c>
     </row>
   </sheetData>
